--- a/CBT_2024_2회/산업안전기사_2024_2회_문항등록.xlsx
+++ b/CBT_2024_2회/산업안전기사_2024_2회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1471,17 +1471,17 @@
       </c>
       <c r="AG3" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;훈련에만 전념할 수 있는&lt;/strong&gt; 것이 Off JT 의 장점이다. 일터를 떠나 있으므로 &lt;strong&gt;일에 끌려다니지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 상호신뢰와 이해가 깊어진다 · 효과가 곧 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념 · 많은 사람을 한꺼번에 · 전문가 초빙 · 특별한 교재와 설비 · 다른 직장 사람과 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 번에 많이 못 한다 · 상사의 능력에 좌우된다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현장에 바로 맞지 않을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;훈련에만 전념할 수 있는&lt;/strong&gt; 것이 Off JT의 장점이다. 일터를 떠나 있으므로 &lt;strong&gt;일에 끌려다니지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 상호신뢰와 이해가 깊어진다 · 효과가 곧 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념 · 많은 사람을 한꺼번에 · 전문가 초빙 · 특별한 교재와 설비 · 다른 직장 사람과 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 번에 많이 못 한다 · 상사의 능력에 좌우된다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현장에 바로 맞지 않을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH3" s="32" t="inlineStr">
         <is>
-          <t>② 상호신뢰와 이해도가 높아지는 것은 OJT 의 장점이다.&lt;br&gt;③ 개개인에 맞춘 지도훈련도 OJT 다.&lt;br&gt;④ 직장 실정에 맞는 실제적 훈련도 OJT 다.</t>
+          <t>② 상호신뢰와 이해도가 높아지는 것은 OJT의 장점이다.&lt;br&gt;③ 개개인에 맞춘 지도훈련도 OJT다.&lt;br&gt;④ 직장 실정에 맞는 실제적 훈련도 OJT다.</t>
         </is>
       </c>
       <c r="AI3" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「전념 · 많이 · 전문가 · 설비 · 교류」는 Off JT&lt;/strong&gt;, &lt;strong&gt;「맞춤 · 즉시 · 신뢰」는 OJT&lt;/strong&gt;다. 이 낱말 묶음만 잡으면 어느 쪽을 물어도 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전념할 수 있으면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「전념 · 많이 · 전문가 · 설비 · 교류」는 Off JT&lt;/strong&gt;, &lt;strong&gt;「맞춤 · 즉시 · 신뢰」는 OJT&lt;/strong&gt;다. 이 낱말 묶음만 잡으면 어느 쪽을 물어도 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전념할 수 있으면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="AG5" s="32" t="inlineStr">
         <is>
-          <t>흰색은 &lt;strong&gt;N9.5&lt;/strong&gt;다. &lt;strong&gt;N0.5 는 검은색&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전보건표지의 색도기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색채&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색도기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;빨간색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7.5R 4/14&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금지 · 경고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노란색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5Y 8.5/12&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파란색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5PB 4/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;녹색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5G 4/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흰색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;N9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보조색&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밝다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검은색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;N0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보조색&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어둡다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>흰색은 &lt;strong&gt;N9.5&lt;/strong&gt;다. &lt;strong&gt;N0.5는 검은색&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전보건표지의 색도기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색채&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색도기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;빨간색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7.5R 4/14&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금지 · 경고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노란색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5Y 8.5/12&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파란색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5PB 4/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;녹색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5G 4/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흰색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;N9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보조색&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밝다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검은색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;N0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보조색&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어둡다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH5" s="32" t="inlineStr">
         <is>
-          <t>① 빨간색 7.5R 4/14 는 맞다.&lt;br&gt;② 노란색 5Y 8.5/12 도 맞다.&lt;br&gt;③ 파란색 2.5PB 4/10 도 맞다.</t>
+          <t>① 빨간색 7.5R 4/14는 맞다.&lt;br&gt;② 노란색 5Y 8.5/12 도 맞다.&lt;br&gt;③ 파란색 2.5PB 4/10 도 맞다.</t>
         </is>
       </c>
       <c r="AI5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업안전보건법 시행규칙 별표8 — 안전보건표지의 색도기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;N 은 무채색(Neutral)&lt;/strong&gt;을 뜻하고 뒤의 숫자가 &lt;strong&gt;명도&lt;/strong&gt;다. &lt;strong&gt;9.5 는 거의 흰색, 0.5 는 거의 검은색&lt;/strong&gt;이다. 보기 ④는 이 두 값을 서로 바꿔 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;흰색 N9.5, 검은색 N0.5&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행규칙 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 8&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;산업안전보건법 시행규칙 별표8 — 안전보건표지의 색도기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;N은 무채색(Neutral)&lt;/strong&gt;을 뜻하고 뒤의 숫자가 &lt;strong&gt;명도&lt;/strong&gt;다. &lt;strong&gt;9.5는 거의 흰색, 0.5는 거의 검은색&lt;/strong&gt;이다. 보기 ④는 이 두 값을 서로 바꿔 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;흰색 N9.5, 검은색 N0.5&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행규칙 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 8&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AI6" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업안전보건법 제139조 — 유해·위험작업에 대한 근로시간 제한&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;잠함·잠수 작업 같은 고기압 작업&lt;/strong&gt;을 두고 정한 규정이다. &lt;strong&gt;일반 8/40 보다 각각 2시간, 6시간 적은&lt;/strong&gt; 6/34 라는 대비로 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1일 6시간, 1주 34시간&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95/%EC%A0%9C139%EC%A1%B0" target="_blank"&gt;제139조(유해ㆍ위험작업에 대한 근로시간 제한 등)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 유해하거나 위험한 작업으로서 높은 기압에서 하는 작업 등 대통령령으로 정하는 작업에 종사하는 근로자에게는 &lt;strong&gt;1일 6시간, 1주 34시간&lt;/strong&gt;을 초과하여 근로하게 해서는 아니 된다.&lt;br&gt;② 사업주는 대통령령으로 정하는 유해하거나 위험한 작업에 종사하는 근로자에게 필요한 안전조치 및 보건조치 외에 작업과 휴식의 적정한 배분 및 근로시간과 관련된 근로조건의 개선을 통하여 근로자의 건강 보호를 위한 조치를 하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;산업안전보건법 제139조 — 유해·위험작업에 대한 근로시간 제한&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;잠함·잠수 작업 같은 고기압 작업&lt;/strong&gt;을 두고 정한 규정이다. &lt;strong&gt;일반 8/40보다 각각 2시간, 6시간 적은&lt;/strong&gt; 6/34라는 대비로 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1일 6시간, 1주 34시간&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95/%EC%A0%9C139%EC%A1%B0" target="_blank"&gt;제139조(유해ㆍ위험작업에 대한 근로시간 제한 등)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 유해하거나 위험한 작업으로서 높은 기압에서 하는 작업 등 대통령령으로 정하는 작업에 종사하는 근로자에게는 &lt;strong&gt;1일 6시간, 1주 34시간&lt;/strong&gt;을 초과하여 근로하게 해서는 아니 된다.&lt;br&gt;② 사업주는 대통령령으로 정하는 유해하거나 위험한 작업에 종사하는 근로자에게 필요한 안전조치 및 보건조치 외에 작업과 휴식의 적정한 배분 및 근로시간과 관련된 근로조건의 개선을 통하여 근로자의 건강 보호를 위한 조치를 하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AI7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험예지훈련 4라운드&lt;/strong&gt;&lt;br&gt;흐름은 &lt;strong&gt;보고 → 캐고 → 세우고 → 다짐한다&lt;/strong&gt;다. 마지막 4R 에서 &lt;strong&gt;「~를 하자, 좋아!」라고 소리쳐 확인&lt;/strong&gt; 하는 것이 이 훈련의 특징이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현상파악 · 본질추구 · 대책수립 · 행동목표&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험예지훈련 4라운드&lt;/strong&gt;&lt;br&gt;흐름은 &lt;strong&gt;보고 → 캐고 → 세우고 → 다짐한다&lt;/strong&gt;다. 마지막 4R에서 &lt;strong&gt;「~를 하자, 좋아!」라고 소리쳐 확인&lt;/strong&gt;하는 것이 이 훈련의 특징이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현상파악 · 본질추구 · 대책수립 · 행동목표&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AI17" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하인리히의 사고예방대책 기본원리 5단계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;조직이 맨 앞&lt;/strong&gt;이라는 것만 잡아도 보기 둘이 걸러진다. 마지막 단계의 &lt;strong&gt;3E 는 Engineering(기술) · Education(교육) · Enforcement(독려·규제)&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;조 · 사 · 분 · 선 · 적&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하인리히의 사고예방대책 기본원리 5단계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;조직이 맨 앞&lt;/strong&gt;이라는 것만 잡아도 보기 둘이 걸러진다. 마지막 단계의 &lt;strong&gt;3E는 Engineering(기술) · Education(교육) · Enforcement(독려·규제)&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;조 · 사 · 분 · 선 · 적&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OR 게이트&lt;/strong&gt;다. &lt;strong&gt;어느 하나만 일어나도&lt;/strong&gt; 출력이 생기는 &lt;strong&gt;논리합&lt;/strong&gt;의 관계다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 기본 게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;논리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제 출력&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;논리합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어느 하나라도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위가 둥근 방패꼴&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;논리곱&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나야&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아래가 평평한 반원&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 맞을 때만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;육각형&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부정 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;NOT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력의 반대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2024_02_021_exp1.png"&gt;&lt;em&gt;OR 게이트 — 어느 하나만 일어나도 출력이 난다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;OR 게이트&lt;/strong&gt;다. &lt;strong&gt;어느 하나만 일어나도&lt;/strong&gt; 출력이 생기는 &lt;strong&gt;논리합&lt;/strong&gt;의 관계다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 기본 게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;논리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제 출력&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;논리합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어느 하나라도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위가 둥근 방패꼴&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;논리곱&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나야&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아래가 평평한 반원&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 맞을 때만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;육각형&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부정 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;NOT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력의 반대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2024_02_021_exp1.png"&gt;&lt;em&gt;OR 게이트 — 어느 하나만 일어나도 출력이 난다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 논리 게이트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;논리합(OR)은 「또는」, 논리곱(AND)은 「그리고」&lt;/strong&gt;다. 확률로는 &lt;strong&gt;OR 는 &lt;/strong&gt;$1 - ( 1 - P_{1} ) ( 1 - P_{2} )$&lt;strong&gt;, AND 는 &lt;/strong&gt;$P_{1} P_{2}$다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;어느 하나라도면 OR&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 논리 게이트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;논리합(OR)은 「또는」, 논리곱(AND)은 「그리고」&lt;/strong&gt;다. 확률로는 &lt;strong&gt;OR는 &lt;/strong&gt;$1 - ( 1 - P_{1} ) ( 1 - P_{2} )$&lt;strong&gt;, AND는 &lt;/strong&gt;$P_{1} P_{2}$다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;어느 하나라도면 OR&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4176,17 +4176,17 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>위가 둥근 방패꼴이므로 &lt;strong&gt;OR 게이트&lt;/strong&gt;다. $A = 1 - ( 1 - 0.3 ) ( 1 - 0.2 ) ( 1 - 0.2 ) = 1 - 0.7 \times 0.8 \times 0.8 = 1 - 0.448 = 0.552$ 다.</t>
+          <t>위가 둥근 방패꼴이므로 &lt;strong&gt;OR 게이트&lt;/strong&gt;다. $A = 1 - ( 1 - 0.3 ) ( 1 - 0.2 ) ( 1 - 0.2 ) = 1 - 0.7 \times 0.8 \times 0.8 = 1 - 0.448 = 0.552$다.</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>① 0.012 는 AND 로 계산한 값($0.3 \times 0.2 \times 0.2$)이다.&lt;br&gt;② 게이트는 AND 가 아니라 OR 다.&lt;br&gt;④ 게이트가 AND 라면 값도 0.552 가 아니다.</t>
+          <t>① 0.012는 AND로 계산한 값($0.3 \times 0.2 \times 0.2$)이다.&lt;br&gt;② 게이트는 AND가 아니라 OR다.&lt;br&gt;④ 게이트가 AND 라면 값도 0.552가 아니다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OR 게이트의 확률 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OR 는 「하나도 안 일어날 확률」을 빼는&lt;/strong&gt; 것이 편하다. &lt;strong&gt;AND 로 풀면 0.012, OR 로 풀면 0.552&lt;/strong&gt;로 값이 크게 달라지므로, &lt;strong&gt;게이트 모양을 먼저 확인&lt;/strong&gt; 해야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;OR 는 여사건으로 계산&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OR 게이트의 확률 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OR는 「하나도 안 일어날 확률」을 빼는&lt;/strong&gt; 것이 편하다. &lt;strong&gt;AND로 풀면 0.012, OR로 풀면 0.552&lt;/strong&gt;로 값이 크게 달라지므로, &lt;strong&gt;게이트 모양을 먼저 확인&lt;/strong&gt;해야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;OR는 여사건으로 계산&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;집 모양 오각형이 통상사상&lt;/strong&gt;이다. 나머지 셋은 모양과 이름이 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 사상기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 분석할 수 있는 사상 · 정상사상과 중간사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 분석할 수 없는 밑바닥 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정보가 없거나 중요하지 않아 더 캐지 않는 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;집 모양 오각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;늘 일어나는 정상적인 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다른 곳으로 이어진다는 표시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;집 모양 오각형이 통상사상&lt;/strong&gt;이다. 나머지 셋은 모양과 이름이 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 사상기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 분석할 수 있는 사상 · 정상사상과 중간사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 분석할 수 없는 밑바닥 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정보가 없거나 중요하지 않아 더 캐지 않는 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;집 모양 오각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;늘 일어나는 정상적인 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다른 곳으로 이어진다는 표시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AI25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 사상기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네모는 캘 수 있는 것, 동그라미는 더 못 캐는 것, 마름모는 캐지 않기로 한 것&lt;/strong&gt;이다. &lt;strong&gt;전이기호는 삼각형&lt;/strong&gt;이고, &lt;strong&gt;집 모양은 늘 있는 일(통상사상)&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;네모는 결함, 원은 기본, 마름모는 생략, 집은 통상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 사상기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네모는 캘 수 있는 것, 동그라미는 더 못 캐는 것, 마름모는 캐지 않기로 한 것&lt;/strong&gt;이다. &lt;strong&gt;전이기호는 삼각형&lt;/strong&gt;이고, &lt;strong&gt;집 모양은 늘 있는 일(통상사상)&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;네모는 결함, 원은 기본, 마름모는 생략, 집은 통상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="U26" s="32" t="inlineStr">
         <is>
-          <t>4m 또는 그보다 먼 물체만을 잘 볼 수 있는 원시 안경은 몇 D 인가? (단, 명시거리는 25cm 로 한다.)</t>
+          <t>4m 또는 그보다 먼 물체만을 잘 볼 수 있는 원시 안경은 몇 D 인가? (단, 명시거리는 25cm로 한다.)</t>
         </is>
       </c>
       <c r="V26" s="32" t="inlineStr"/>
@@ -4430,17 +4430,17 @@
       </c>
       <c r="AG26" s="32" t="inlineStr">
         <is>
-          <t>필요한 굴절력은 $D = \dfrac{1}{0.25} - \dfrac{1}{4} = 4 - 0.25 = 3.75$ [D] 다.</t>
+          <t>필요한 굴절력은 $D = \dfrac{1}{0.25} - \dfrac{1}{4} = 4 - 0.25 = 3.75$ [D]다.</t>
         </is>
       </c>
       <c r="AH26" s="32" t="inlineStr">
         <is>
-          <t>① 1.75 [D] 는 계산과 맞지 않는다.&lt;br&gt;② 2.75 [D] 도 맞지 않는다.&lt;br&gt;④ 4.75 [D] 는 먼 점을 빼지 않은 값에 가깝다.</t>
+          <t>① 1.75 [D]는 계산과 맞지 않는다.&lt;br&gt;② 2.75 [D] 도 맞지 않는다.&lt;br&gt;④ 4.75 [D]는 먼 점을 빼지 않은 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;디옵터(D)&lt;/strong&gt;&lt;br&gt;$D = \dfrac{1}{\text{초점거리} [ m ]}$ 다. &lt;strong&gt;보고 싶은 거리(25 [cm])의 굴절력에서 지금 볼 수 있는 거리(4 [m])의 굴절력을 뺀&lt;/strong&gt; 만큼이 안경의 도수다. &lt;strong&gt;원시는 볼록렌즈라 값이 양수&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D = 1 / 0.25 - 1 / 4$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;디옵터(D)&lt;/strong&gt;&lt;br&gt;$D = \dfrac{1}{\text{초점거리} [ m ]}$다. &lt;strong&gt;보고 싶은 거리(25 [cm])의 굴절력에서 지금 볼 수 있는 거리(4 [m])의 굴절력을 뺀&lt;/strong&gt; 만큼이 안경의 도수다. &lt;strong&gt;원시는 볼록렌즈라 값이 양수&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D = 1 / 0.25 - 1 / 4$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4680,12 +4680,12 @@
       </c>
       <c r="AG28" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;fail-operational&lt;/strong&gt;이다. &lt;strong&gt;고장이 나도 다음 점검 때까지 그대로 운전&lt;/strong&gt; 할 수 있는 가장 안전한 방식이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;페일세이프의 세 단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;고장이 나면&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;fail-passive&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;장치가 멈춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일반 기계의 정지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;fail-active&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경보를 내며 잠시 운전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경보 후 정지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;fail-operational&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다음 점검까지 그대로 운전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;병렬 여분계통 · 항공기 엔진&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;fail-operational&lt;/strong&gt;이다. &lt;strong&gt;고장이 나도 다음 점검 때까지 그대로 운전&lt;/strong&gt;할 수 있는 가장 안전한 방식이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;페일세이프의 세 단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;고장이 나면&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;fail-passive&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;장치가 멈춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일반 기계의 정지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;fail-active&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경보를 내며 잠시 운전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경보 후 정지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;fail-operational&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다음 점검까지 그대로 운전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;병렬 여분계통 · 항공기 엔진&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
-          <t>① fail-soft 는 성능을 낮춰 이어 가는 방식으로 페일세이프의 정식 세 단계에는 들지 않는다.&lt;br&gt;② fail-active 는 경보를 내며 잠시만 운전한다.&lt;br&gt;③ fail-passive 는 곧바로 멈춘다.</t>
+          <t>① fail-soft는 성능을 낮춰 이어 가는 방식으로 페일세이프의 정식 세 단계에는 들지 않는다.&lt;br&gt;② fail-active는 경보를 내며 잠시만 운전한다.&lt;br&gt;③ fail-passive는 곧바로 멈춘다.</t>
         </is>
       </c>
       <c r="AI28" s="32" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「고장의 영향 크기」&lt;/strong&gt;라는 평가요소는 따로 없다. 다섯은 &lt;strong&gt;기능적 고장 영향의 중요도 · 영향을 미치는 시스템의 범위 · 고장발생의 빈도 · 고장방지의 가능성 · 신규 설계의 정도&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA 의 고장등급 평가요소 다섯&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;평가요소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능적 고장 영향의 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₁&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영향을 미치는 시스템의 범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₂&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장발생의 빈도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₃&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장방지의 가능성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₄&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신규 설계의 정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₅&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「고장의 영향 크기」&lt;/strong&gt;라는 평가요소는 따로 없다. 다섯은 &lt;strong&gt;기능적 고장 영향의 중요도 · 영향을 미치는 시스템의 범위 · 고장발생의 빈도 · 고장방지의 가능성 · 신규 설계의 정도&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA의 고장등급 평가요소 다섯&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;평가요소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능적 고장 영향의 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₁&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영향을 미치는 시스템의 범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₂&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장발생의 빈도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₃&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장방지의 가능성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₄&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신규 설계의 정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C₅&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA 의 고장등급 평가&lt;/strong&gt;&lt;br&gt;다섯 요소를 곱해 $C = ( C_{1} C_{2} C_{3} C_{4} C_{5} )^{1 / 5}$로 치명도를 매긴다. &lt;strong&gt;「영향의 크기」는 「영향의 중요도」·「영향 범위」와 겹쳐 보이지만 정식 항목이 아니다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;중요도 · 범위 · 빈도 · 방지 가능성 · 신규성&lt;/u&gt; 다섯.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA의 고장등급 평가&lt;/strong&gt;&lt;br&gt;다섯 요소를 곱해 $C = ( C_{1} C_{2} C_{3} C_{4} C_{5} )^{1 / 5}$로 치명도를 매긴다. &lt;strong&gt;「영향의 크기」는 「영향의 중요도」·「영향 범위」와 겹쳐 보이지만 정식 항목이 아니다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;중요도 · 범위 · 빈도 · 방지 가능성 · 신규성&lt;/u&gt; 다섯.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5059,17 +5059,17 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;신뢰성 분석비용&lt;/strong&gt;은 SSPP 에 담을 항목이 아니다. &lt;strong&gt;돈 계산은 안전계획의 내용이 아니다&lt;/strong&gt;.</t>
+          <t>&lt;strong&gt;신뢰성 분석비용&lt;/strong&gt;은 SSPP에 담을 항목이 아니다. &lt;strong&gt;돈 계산은 안전계획의 내용이 아니다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① 안전조직은 SSPP 에 담는다.&lt;br&gt;② 안전성의 평가도 그렇다.&lt;br&gt;③ 안전자료의 수집과 갱신도 그렇다.</t>
+          <t>① 안전조직은 SSPP에 담는다.&lt;br&gt;② 안전성의 평가도 그렇다.&lt;br&gt;③ 안전자료의 수집과 갱신도 그렇다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시스템 안전 프로그램 계획(SSPP)&lt;/strong&gt;&lt;br&gt;아홉 항목은 &lt;strong&gt;계획의 개요 · 안전조직 · 계약조건 · 관련 부문과의 조정 · 안전기준 · 안전해석 · 안전성 평가 · 안전데이터의 수집과 분석 · 경과와 결과의 분석&lt;/strong&gt;이다. &lt;strong&gt;「비용」이 들어간 보기는 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비용은 SSPP 의 항목이 아니다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;시스템 안전 프로그램 계획(SSPP)&lt;/strong&gt;&lt;br&gt;아홉 항목은 &lt;strong&gt;계획의 개요 · 안전조직 · 계약조건 · 관련 부문과의 조정 · 안전기준 · 안전해석 · 안전성 평가 · 안전데이터의 수집과 분석 · 경과와 결과의 분석&lt;/strong&gt;이다. &lt;strong&gt;「비용」이 들어간 보기는 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비용은 SSPP의 항목이 아니다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조종장치로 기계를 통제&lt;/strong&gt; 하는 것은 &lt;strong&gt;수동 또는 기계화 시스템&lt;/strong&gt;에서 사람이 하는 일이다. 자동화 시스템에서는 기계가 스스로 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인간-기계 시스템의 세 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;체계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사람이 하는 일&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수동 체계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;동력원과 제어를 모두&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수공구&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기계화(반자동) 체계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;동력은 기계, 제어는 사람&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공작기계 · 자동차 운전&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자동 체계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감시 · 프로그래밍 · 보전 · 계획 수립&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;자동화 공장 · 자동교환기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;조종장치로 기계를 통제&lt;/strong&gt;하는 것은 &lt;strong&gt;수동 또는 기계화 시스템&lt;/strong&gt;에서 사람이 하는 일이다. 자동화 시스템에서는 기계가 스스로 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인간-기계 시스템의 세 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;체계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사람이 하는 일&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수동 체계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;동력원과 제어를 모두&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수공구&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기계화(반자동) 체계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;동력은 기계, 제어는 사람&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공작기계 · 자동차 운전&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자동 체계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감시 · 프로그래밍 · 보전 · 계획 수립&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;자동화 공장 · 자동교환기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="AH35" s="32" t="inlineStr">
         <is>
-          <t>① 들기 빈도는 FM 으로 고려한다.&lt;br&gt;③ 손잡이 형상은 CM 으로 고려한다.&lt;br&gt;④ 허리 비대칭 각도는 AM 으로 고려한다.</t>
+          <t>① 들기 빈도는 FM으로 고려한다.&lt;br&gt;③ 손잡이 형상은 CM으로 고려한다.&lt;br&gt;④ 허리 비대칭 각도는 AM으로 고려한다.</t>
         </is>
       </c>
       <c r="AI35" s="32" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① FHA 는 분담 설계에서 다른 곳의 영향을 보는 기법이다.&lt;br&gt;③ FTA 는 정량적·연역적 기법이다.&lt;br&gt;④ FMEA 는 설계 단계의 귀납적 기법이다.</t>
+          <t>① FHA는 분담 설계에서 다른 곳의 영향을 보는 기법이다.&lt;br&gt;③ FTA는 정량적·연역적 기법이다.&lt;br&gt;④ FMEA는 설계 단계의 귀납적 기법이다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;PHA(예비위험분석)&lt;/strong&gt;&lt;br&gt;PHA 는 위험을 네 등급으로 나눈다 — &lt;strong&gt;파국(catastrophic) · 중대(critical) · 한계(marginal) · 무시가능(negligible)&lt;/strong&gt;. &lt;strong&gt;「최초 단계」·「정성적」&lt;/strong&gt; 두 낱말이 PHA 를 가리킨다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맨 처음의 정성적 해석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;PHA(예비위험분석)&lt;/strong&gt;&lt;br&gt;PHA는 위험을 네 등급으로 나눈다 — &lt;strong&gt;파국(catastrophic) · 중대(critical) · 한계(marginal) · 무시가능(negligible)&lt;/strong&gt;. &lt;strong&gt;「최초 단계」·「정성적」&lt;/strong&gt; 두 낱말이 PHA를 가리킨다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맨 처음의 정성적 해석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6095,17 +6095,17 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1,000 [Hz]&lt;/strong&gt;다. &lt;strong&gt;1,000 [Hz] 순음의 음압수준 [dB] 값을 그대로 phon&lt;/strong&gt;으로 삼는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음량의 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정의&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz] 순음의 음압수준 [dB] 과 같게 들리는 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기준은 1,000 [Hz]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [phon] 을 1 [sone] 으로 삼은 비율 척도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\mathrm{sone} = 2^{( \mathrm{phon} - 40 ) / 10}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 [phon] 이 오를 때마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;sone 은 2배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;크기가 두 배로 들린다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1,000 [Hz]&lt;/strong&gt;다. &lt;strong&gt;1,000 [Hz] 순음의 음압수준 [dB] 값을 그대로 phon&lt;/strong&gt;으로 삼는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음량의 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정의&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz] 순음의 음압수준 [dB]과 같게 들리는 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기준은 1,000 [Hz]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [phon]을 1 [sone]으로 삼은 비율 척도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\mathrm{sone} = 2^{( \mathrm{phon} - 40 ) / 10}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 [phon]이 오를 때마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;sone은 2배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;크기가 두 배로 들린다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>② 2,000 [Hz] 는 기준 주파수가 아니다.&lt;br&gt;③ 3,000 [Hz] 도 아니다.&lt;br&gt;④ 4,000 [Hz] 는 사람 귀가 가장 예민한 대역이지 phon 의 기준은 아니다.</t>
+          <t>② 2,000 [Hz]는 기준 주파수가 아니다.&lt;br&gt;③ 3,000 [Hz] 도 아니다.&lt;br&gt;④ 4,000 [Hz]는 사람 귀가 가장 예민한 대역이지 phon의 기준은 아니다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;phon 과 sone&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;phon 은 「몇 [dB] 처럼 들리는가」, sone 은 「몇 배로 들리는가」&lt;/strong&gt;다. &lt;strong&gt;40 [phon] = 1 [sone]&lt;/strong&gt;을 기준으로 &lt;strong&gt;10 [phon] 마다 두 배&lt;/strong&gt;가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;phon 의 기준은 1,000 [Hz]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;phon과 sone&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;phon은 「몇 [dB] 처럼 들리는가」, sone은 「몇 배로 들리는가」&lt;/strong&gt;다. &lt;strong&gt;40 [phon] = 1 [sone]&lt;/strong&gt;을 기준으로 &lt;strong&gt;10 [phon] 마다 두 배&lt;/strong&gt;가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;phon의 기준은 1,000 [Hz]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제2단계 정성적 평가&lt;/strong&gt;다. &lt;strong&gt;입지조건과 공장 내 배치&lt;/strong&gt;는 설계 관계의 정성적 항목이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;화학설비 안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계자료의 작성 준비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;입지조건 도면 · 공정계통도 · 물질 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 관계 — 입지조건 · 공장 내 배치 · 건조물 · 소방설비&lt;/u&gt; / 운전 관계 — 원재료 · 공정 · 수송·저장&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;취급물질 · 용량 · 온도 · 압력 · 조작&lt;/u&gt; 다섯&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비 대책 · 관리적 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA 에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;제2단계 정성적 평가&lt;/strong&gt;다. &lt;strong&gt;입지조건과 공장 내 배치&lt;/strong&gt;는 설계 관계의 정성적 항목이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;화학설비 안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계자료의 작성 준비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;입지조건 도면 · 공정계통도 · 물질 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 관계 — 입지조건 · 공장 내 배치 · 건조물 · 소방설비&lt;/u&gt; / 운전 관계 — 원재료 · 공정 · 수송·저장&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;취급물질 · 용량 · 온도 · 압력 · 조작&lt;/u&gt; 다섯&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비 대책 · 관리적 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="U42" s="32" t="inlineStr">
         <is>
-          <t>첨단 경보기시스템의 고장율은 0이다. 경계의 효과로 조작자 오류율은 0.01t/hr 이며, 인간의 실수율은 균질(homogeneous)한 것으로 가정한다. 또한, 이 시스템의 스위치 조작자는 1시간마다 스위치를 작동해야 하는데 인간오류확률(HEP: Human Error Probability)이 0.001 인 경우에 2시간에서 6시간 사이에 인간-기계 시스템의 신뢰도는 약 얼마인가?</t>
+          <t>첨단 경보기시스템의 고장율은 0이다. 경계의 효과로 조작자 오류율은 0.01t/hr이며, 인간의 실수율은 균질(homogeneous)한 것으로 가정한다. 또한, 이 시스템의 스위치 조작자는 1시간마다 스위치를 작동해야 하는데 인간오류확률(HEP: Human Error Probability)이 0.001 인 경우에 2시간에서 6시간 사이에 인간-기계 시스템의 신뢰도는 약 얼마인가?</t>
         </is>
       </c>
       <c r="V42" s="32" t="inlineStr"/>
@@ -6482,12 +6482,12 @@
       </c>
       <c r="AG42" s="32" t="inlineStr">
         <is>
-          <t>경계 효과에 따른 신뢰도는 $R_{1} = e^{-0.01 \times 4} = e^{-0.04} \fallingdotseq 0.9608$ 이다. 스위치는 &lt;strong&gt;2·3·4·5시 네 번&lt;/strong&gt; 작동하므로 $R_{2} = ( 1 - 0.001 )^{4} \fallingdotseq 0.996$ 이다. 전체는 $0.9608 \times 0.996 \fallingdotseq 0.957$ 이다.</t>
+          <t>경계 효과에 따른 신뢰도는 $R_{1} = e^{-0.01 \times 4} = e^{-0.04} \fallingdotseq 0.9608$이다. 스위치는 &lt;strong&gt;2·3·4·5시 네 번&lt;/strong&gt; 작동하므로 $R_{2} = ( 1 - 0.001 )^{4} \fallingdotseq 0.996$이다. 전체는 $0.9608 \times 0.996 \fallingdotseq 0.957$이다.</t>
         </is>
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
-          <t>① 0.938 은 계산과 맞지 않는다.&lt;br&gt;② 0.948 도 맞지 않는다.&lt;br&gt;④ 0.967 도 맞지 않는다.</t>
+          <t>① 0.938은 계산과 맞지 않는다.&lt;br&gt;② 0.948 도 맞지 않는다.&lt;br&gt;④ 0.967 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI42" s="32" t="inlineStr">
@@ -6740,17 +6740,17 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>플랜지 지름은 &lt;strong&gt;숫돌 바깥지름의 1/3 이상&lt;/strong&gt;이므로 $150 \times 1 / 3 = 50$ [mm] 다.</t>
+          <t>플랜지 지름은 &lt;strong&gt;숫돌 바깥지름의 1/3 이상&lt;/strong&gt;이므로 $150 \times 1 / 3 = 50$ [mm]다.</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>① 25 [mm] 는 1/6 로 기준에 못 미친다.&lt;br&gt;③ 75 [mm] 는 1/2 로 기준보다 크다.&lt;br&gt;④ 100 [mm] 는 2/3 로 기준보다 훨씬 크다.</t>
+          <t>① 25 [mm]는 1/6로 기준에 못 미친다.&lt;br&gt;③ 75 [mm]는 1/2로 기준보다 크다.&lt;br&gt;④ 100 [mm]는 2/3로 기준보다 훨씬 크다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연삭숫돌의 플랜지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/strong&gt; 이라야 숫돌을 제대로 붙들어 파괴를 막는다. 연삭기는 이 밖에 &lt;strong&gt;작업 시작 전 1분, 숫돌 교체 뒤 3분 시운전&lt;/strong&gt;과 &lt;strong&gt;최고사용 원주속도 초과 금지&lt;/strong&gt;가 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연삭숫돌의 플랜지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/strong&gt;이라야 숫돌을 제대로 붙들어 파괴를 막는다. 연삭기는 이 밖에 &lt;strong&gt;작업 시작 전 1분, 숫돌 교체 뒤 3분 시운전&lt;/strong&gt;과 &lt;strong&gt;최고사용 원주속도 초과 금지&lt;/strong&gt;가 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플랜지는 숫돌 지름의 1/3 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="AG46" s="32" t="inlineStr">
         <is>
-          <t>비전동체이므로 $Y = 6 + 0.15 X = 6 + 0.15 \times 60 = 6 + 9 = 15$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가드 개구부 간격의 식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.1 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 760$&lt;u&gt; [mm] 일 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 비전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.15 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 160$&lt;u&gt; [mm] 일 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 30$&lt;u&gt; [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X \ge 160$ [mm] 이면&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>비전동체이므로 $Y = 6 + 0.15 X = 6 + 0.15 \times 60 = 6 + 9 = 15$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가드 개구부 간격의 식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.1 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 760$&lt;u&gt; [mm] 일 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 비전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.15 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 160$&lt;u&gt; [mm] 일 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 30$&lt;u&gt; [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X \ge 160$ [mm] 이면&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH46" s="32" t="inlineStr">
         <is>
-          <t>① 6 [mm] 는 거리를 0 으로 놓았을 때의 값이다.&lt;br&gt;② 10 [mm] 는 계산과 맞지 않는다.&lt;br&gt;④ 18 [mm] 도 맞지 않는다.</t>
+          <t>① 6 [mm]는 거리를 0으로 놓았을 때의 값이다.&lt;br&gt;② 10 [mm]는 계산과 맞지 않는다.&lt;br&gt;④ 18 [mm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI46" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가드 개구부 간격(ISO 및 안전인증 기준)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;6 [mm] 는 손가락이 들어가지 못하는 최소값&lt;/strong&gt;이고, &lt;strong&gt;거리에 비례해 조금씩 넓혀 준다&lt;/strong&gt;. &lt;strong&gt;전동체는 0.1, 비전동체는 0.15&lt;/strong&gt;라는 계수 차이가 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비전동체는 &lt;/u&gt;$6 + 0.15 X$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가드 개구부 간격(ISO 및 안전인증 기준)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;6 [mm]는 손가락이 들어가지 못하는 최소값&lt;/strong&gt;이고, &lt;strong&gt;거리에 비례해 조금씩 넓혀 준다&lt;/strong&gt;. &lt;strong&gt;전동체는 0.1, 비전동체는 0.15&lt;/strong&gt;라는 계수 차이가 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비전동체는 &lt;/u&gt;$6 + 0.15 X$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AG48" s="32" t="inlineStr">
         <is>
-          <t>$\text{안전율} = \dfrac{\text{기초강도} ( \text{인장강도} )}{\text{허용응력}}$ 다. &lt;strong&gt;센 쪽을 위에, 견디게 할 쪽을 아래에&lt;/strong&gt; 둔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전율의 여러 표현&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\text{안전율} = \dfrac{\text{기초강도}}{\text{허용응력}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 기본&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\text{안전율} = \dfrac{\text{극한강도}}{\text{최대 설계응력}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\text{안전율} = \dfrac{\text{파단하중}}{\text{최대 사용하중}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\text{안전율} = \dfrac{\text{극한하중}}{\text{정격하중}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\text{안전율} = \dfrac{\text{기초강도} ( \text{인장강도} )}{\text{허용응력}}$다. &lt;strong&gt;센 쪽을 위에, 견디게 할 쪽을 아래에&lt;/strong&gt; 둔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전율의 여러 표현&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\text{안전율} = \dfrac{\text{기초강도}}{\text{허용응력}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 기본&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\text{안전율} = \dfrac{\text{극한강도}}{\text{최대 설계응력}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\text{안전율} = \dfrac{\text{파단하중}}{\text{최대 사용하중}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\text{안전율} = \dfrac{\text{극한하중}}{\text{정격하중}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH48" s="32" t="inlineStr">
@@ -7514,17 +7514,17 @@
       </c>
       <c r="AG50" s="32" t="inlineStr">
         <is>
-          <t>$\text{극한하중} = \text{안전계수} \times \text{최대설계하중} = 5 \times 1 {,} 000 = 5 {,} 000$ [N] 이다.</t>
+          <t>$\text{극한하중} = \text{안전계수} \times \text{최대설계하중} = 5 \times 1 {,} 000 = 5 {,} 000$ [N]이다.</t>
         </is>
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>① 200 [N] 은 나누어 버린 값이다.&lt;br&gt;② 2,000 [N] 은 계산과 맞지 않는다.&lt;br&gt;④ 12,000 [N] 도 맞지 않는다.</t>
+          <t>① 200 [N]은 나누어 버린 값이다.&lt;br&gt;② 2,000 [N]은 계산과 맞지 않는다.&lt;br&gt;④ 12,000 [N] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전계수와 극한하중&lt;/strong&gt;&lt;br&gt;$\text{안전계수} = \dfrac{\text{극한하중}}{\text{최대설계하중}}$ 이므로 &lt;strong&gt;극한하중은 곱셈&lt;/strong&gt;으로 구한다. 46번과 짝을 이루는 문항으로, &lt;strong&gt;분자·분모 방향만 헷갈리지 않으면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;극한하중 = 안전계수 × 설계하중&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전계수와 극한하중&lt;/strong&gt;&lt;br&gt;$\text{안전계수} = \dfrac{\text{극한하중}}{\text{최대설계하중}}$이므로 &lt;strong&gt;극한하중은 곱셈&lt;/strong&gt;으로 구한다. 46번과 짝을 이루는 문항으로, &lt;strong&gt;분자·분모 방향만 헷갈리지 않으면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;극한하중 = 안전계수 × 설계하중&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="AG53" s="32" t="inlineStr">
         <is>
-          <t>허용응력은 $70 / 2 = 35$ [MPa] = 35 [N/㎟] 다. 최대하중은 $35 \times 1 {,} 800 = 63 {,} 000$ [N] 이므로 &lt;strong&gt;63 [kN]&lt;/strong&gt;이다.</t>
+          <t>허용응력은 $70 / 2 = 35$ [MPa] = 35 [N/㎟]다. 최대하중은 $35 \times 1 {,} 800 = 63 {,} 000$ [N]이므로 &lt;strong&gt;63 [kN]&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
-          <t>① 6.3 [kN] 은 자릿수가 열 배 어긋난다.&lt;br&gt;② 126 [kN] 은 안전율을 나누지 않은 값이다.&lt;br&gt;④ 12.6 [kN] 도 자릿수가 어긋난다.</t>
+          <t>① 6.3 [kN]은 자릿수가 열 배 어긋난다.&lt;br&gt;② 126 [kN]은 안전율을 나누지 않은 값이다.&lt;br&gt;④ 12.6 [kN] 도 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI53" s="32" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="AG56" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;천장은 가벼운 불연성 재료&lt;/strong&gt; 라야 한다. 벽만 견고한 구조로 하고, &lt;strong&gt;천장까지 콘크리트로 막으면 폭발 압력이 빠져나갈 곳이 없다&lt;/strong&gt;.</t>
+          <t>&lt;strong&gt;천장은 가벼운 불연성 재료&lt;/strong&gt;라야 한다. 벽만 견고한 구조로 하고, &lt;strong&gt;천장까지 콘크리트로 막으면 폭발 압력이 빠져나갈 곳이 없다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH56" s="32" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공칭지름의 7 [%] 를 넘게 줄어들면&lt;/strong&gt; 폐기한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제166조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%] 를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;공칭지름의 7 [%]를 넘게 줄어들면&lt;/strong&gt; 폐기한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제166조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%]를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="AG62" s="32" t="inlineStr">
         <is>
-          <t>무릎조작식은 &lt;strong&gt;밑면에서 0.6 [m] 이내&lt;/strong&gt;다. 0.8 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;롤러기 급정지장치 조작부의 위치 (규칙 제148조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설치 위치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손 조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑면에서 1.8 [m] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;복부 조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑면에서 0.8 [m] 이상 1.1 [m] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무릎 조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑면에서 0.6 [m] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.8 [m] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>무릎조작식은 &lt;strong&gt;밑면에서 0.6 [m] 이내&lt;/strong&gt;다. 0.8 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;롤러기 급정지장치 조작부의 위치 (규칙 제148조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설치 위치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손 조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑면에서 1.8 [m] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;복부 조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑면에서 0.8 [m] 이상 1.1 [m] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무릎 조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑면에서 0.6 [m] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.8 [m]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH62" s="32" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="AI62" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제148조 — 급정지장치의 조작부&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;손(1.8) → 배(0.8 ~ 1.1) → 무릎(0.6)&lt;/strong&gt; 순으로 &lt;strong&gt;몸의 높이를 따라 내려간다&lt;/strong&gt;. &lt;strong&gt;복부의 아래끝 0.8 을 무릎 값으로 옮겨 놓는 것&lt;/strong&gt;이 이 문항의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;손 1.8 · 복부 0.8~1.1 · 무릎 0.6&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C148%EC%A1%B0" target="_blank"&gt;제148조(안전밸브의 조정)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제148조(안전밸브의 조정) 사업주는 유압을 동력으로 사용하는 이동식 크레인의 과도한 압력상승을 방지하기 위한 안전밸브에 대하여 최대의 정격하중을 건 때의 압력 이하로 작동되도록 조정하여야 한다. 다만, 하중시험 또는 안전도시험을 실시할 때에 시험하중에 맞는 압력으로 작동될 수 있도록 조정한 경우에는 그러하지 아니하다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제148조 — 급정지장치의 조작부&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;손(1.8) → 배(0.8 ~ 1.1) → 무릎(0.6)&lt;/strong&gt; 순으로 &lt;strong&gt;몸의 높이를 따라 내려간다&lt;/strong&gt;. &lt;strong&gt;복부의 아래끝 0.8을 무릎 값으로 옮겨 놓는 것&lt;/strong&gt;이 이 문항의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;손 1.8 · 복부 0.8~1.1 · 무릎 0.6&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C148%EC%A1%B0" target="_blank"&gt;제148조(안전밸브의 조정)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제148조(안전밸브의 조정) 사업주는 유압을 동력으로 사용하는 이동식 크레인의 과도한 압력상승을 방지하기 위한 안전밸브에 대하여 최대의 정격하중을 건 때의 압력 이하로 작동되도록 조정하여야 한다. 다만, 하중시험 또는 안전도시험을 실시할 때에 시험하중에 맞는 압력으로 작동될 수 있도록 조정한 경우에는 그러하지 아니하다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -9195,12 +9195,12 @@
       </c>
       <c r="AG63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;30 [mA], 0.1초&lt;/strong&gt;다. 감전의 위험한계는 &lt;strong&gt;전류 × 시간 = 50 [mA·s]&lt;/strong&gt; 인데, $30 \times 0.1 = 3$ [mA·s] 로 넉넉히 아래에 든다. 60 [mA] 이상은 &lt;strong&gt;심실세동 영역&lt;/strong&gt;에 들어 위험하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;통전전류의 크기와 인체 반응&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;몸에 일어나는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;약 1 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소감지전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;찌릿함을 느낀다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;7 ~ 8 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고통한계전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;견딜 수는 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 ~ 15 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가수전류(이탈전류)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스스로 손을 뗄 수 있는 한계&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;20 ~ 50 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불수전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육이 굳어 손을 못 뗀다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [mA] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;목숨이 위태롭다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;30 [mA], 0.1초&lt;/strong&gt;다. 감전의 위험한계는 &lt;strong&gt;전류 × 시간 = 50 [mA·s]&lt;/strong&gt; 인데, $30 \times 0.1 = 3$ [mA·s]로 넉넉히 아래에 든다. 60 [mA] 이상은 &lt;strong&gt;심실세동 영역&lt;/strong&gt;에 들어 위험하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;통전전류의 크기와 인체 반응&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;몸에 일어나는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;약 1 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소감지전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;찌릿함을 느낀다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;7 ~ 8 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고통한계전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;견딜 수는 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 ~ 15 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가수전류(이탈전류)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스스로 손을 뗄 수 있는 한계&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;20 ~ 50 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불수전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육이 굳어 손을 못 뗀다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [mA] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;목숨이 위태롭다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>② 60 [mA] 는 심실세동 영역에 들어 안전하지 않다.&lt;br&gt;③ 90 [mA] 도 마찬가지다.&lt;br&gt;④ 120 [mA] 도 마찬가지다.</t>
+          <t>② 60 [mA]는 심실세동 영역에 들어 안전하지 않다.&lt;br&gt;③ 90 [mA] 도 마찬가지다.&lt;br&gt;④ 120 [mA] 도 마찬가지다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="AH65" s="32" t="inlineStr">
         <is>
-          <t>① 15 ~ 20 [mA] 는 불수전류 영역에 가깝다.&lt;br&gt;② 10 ~ 15 [mA] 는 가수전류(이탈전류)다.&lt;br&gt;④ 1 [mA] 는 최소감지전류다.</t>
+          <t>① 15 ~ 20 [mA]는 불수전류 영역에 가깝다.&lt;br&gt;② 10 ~ 15 [mA]는 가수전류(이탈전류)다.&lt;br&gt;④ 1 [mA]는 최소감지전류다.</t>
         </is>
       </c>
       <c r="AI65" s="32" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;배선용차단기(MCCB)&lt;/strong&gt;는 &lt;strong&gt;과전류&lt;/strong&gt;를 끊는 장치다. 누전에는 &lt;strong&gt;누전차단기(ELB)&lt;/strong&gt;를 써야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전에 의한 감전 방지대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보호접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새는 전류를 땅으로 보낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누전차단기(ELB)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새면 곧바로 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;MCCB 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전전압(30 [V] 이하)의 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;애초에 위험한 전압을 쓰지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비접지식 전로의 채용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;돌아갈 길을 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이중절연기기의 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;절연을 두 겹으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;배선용차단기(MCCB)&lt;/strong&gt;는 &lt;strong&gt;과전류&lt;/strong&gt;를 끊는 장치다. 누전에는 &lt;strong&gt;누전차단기(ELB)&lt;/strong&gt;를 써야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전에 의한 감전 방지대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보호접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새는 전류를 땅으로 보낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누전차단기(ELB)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새면 곧바로 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;MCCB가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전전압(30 [V] 이하)의 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;애초에 위험한 전압을 쓰지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비접지식 전로의 채용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;돌아갈 길을 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이중절연기기의 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;절연을 두 겹으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누전에 의한 감전의 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;MCCB 는 「많이 흐르면」, ELB 는 「새면」&lt;/strong&gt; 끊는다. &lt;strong&gt;누전 전류는 수십 [mA] 에 지나지 않아 MCCB 로는 감지되지 않는다&lt;/strong&gt; — 그래서 서로 대신하지 못한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누전은 ELB, 과전류는 MCCB&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누전에 의한 감전의 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;MCCB는 「많이 흐르면」, ELB는 「새면」&lt;/strong&gt; 끊는다. &lt;strong&gt;누전 전류는 수십 [mA]에 지나지 않아 MCCB 로는 감지되지 않는다&lt;/strong&gt; — 그래서 서로 대신하지 못한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누전은 ELB, 과전류는 MCCB&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AH68" s="32" t="inlineStr">
         <is>
-          <t>① 전선관이 충분히 지락전류를 흘릴 수 있으면 본딩을 생략할 수 있다.&lt;br&gt;③ 접지선의 절연피복은 흰색이나 검정색이 아니라 녹색 또는 녹황 줄무늬다.&lt;br&gt;④ 접지선은 1,000 [V] 가 아니라 600 [V] 비닐절연전선 이상이면 된다.</t>
+          <t>① 전선관이 충분히 지락전류를 흘릴 수 있으면 본딩을 생략할 수 있다.&lt;br&gt;③ 접지선의 절연피복은 흰색이나 검정색이 아니라 녹색 또는 녹황 줄무늬다.&lt;br&gt;④ 접지선은 1,000 [V]가 아니라 600 [V] 비닐절연전선 이상이면 된다.</t>
         </is>
       </c>
       <c r="AI68" s="32" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 직류 저압은 700 [V] 가 아니라 1,500 [V] 이하다.&lt;br&gt;③ 직류 고압은 800 [V] 가 아니라 1,500 [V] 초과 7,000 [V] 이하다.&lt;br&gt;④ 교류 고압은 700 [V] 가 아니라 1,000 [V] 초과 7,000 [V] 이하다.</t>
+          <t>① 직류 저압은 700 [V]가 아니라 1,500 [V] 이하다.&lt;br&gt;③ 직류 고압은 800 [V]가 아니라 1,500 [V] 초과 7,000 [V] 이하다.&lt;br&gt;④ 교류 고압은 700 [V]가 아니라 1,000 [V] 초과 7,000 [V] 이하다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AI72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;스파크에 의한 화재의 방지&lt;/strong&gt;&lt;br&gt;유입 개폐기 안에는 &lt;strong&gt;기름(절연유)&lt;/strong&gt;이 들어 있어 &lt;strong&gt;불이 나면 크게 번진다&lt;/strong&gt;. 그래서 &lt;strong&gt;내화벽&lt;/strong&gt;을 두른다. &lt;strong&gt;「내수」와 「내화」&lt;/strong&gt; 한 글자를 바꿔 놓은 것이 이 문항의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;유입 개폐기 둘레에는 내화벽&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;스파크에 의한 화재의 방지&lt;/strong&gt;&lt;br&gt;유입 개폐기 안에는 &lt;strong&gt;기름(절연유)&lt;/strong&gt;이 들어 있어 &lt;strong&gt;불이 나면 크게 번진다&lt;/strong&gt;. 그래서 &lt;strong&gt;내화벽&lt;/strong&gt;을 두른다. &lt;strong&gt;「내수」와 「내화」&lt;/strong&gt;한 글자를 바꿔 놓은 것이 이 문항의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;유입 개폐기 둘레에는 내화벽&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10598,17 +10598,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$F = \dfrac{1}{4 \pi \varepsilon_{0}} \times \dfrac{Q_{1} Q_{2}}{r^{2}} = 9 \times 10^{9} \times \dfrac{1 \times 1}{1^{2}} = 9 \times 10^{9}$ [N] 이다.</t>
+          <t>$F = \dfrac{1}{4 \pi \varepsilon_{0}} \times \dfrac{Q_{1} Q_{2}}{r^{2}} = 9 \times 10^{9} \times \dfrac{1 \times 1}{1^{2}} = 9 \times 10^{9}$ [N]이다.</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① $8.854 \times 10^{-12}$ 는 진공의 유전율 $\varepsilon_{0}$ 값이다.&lt;br&gt;② 1.0 [N] 은 계산과 맞지 않는다.&lt;br&gt;③ $3 \times 10^{3}$ [N] 도 맞지 않는다.</t>
+          <t>① $8.854 \times 10^{-12}$는 진공의 유전율 $\varepsilon_{0}$ 값이다.&lt;br&gt;② 1.0 [N]은 계산과 맞지 않는다.&lt;br&gt;③ $3 \times 10^{3}$ [N] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;쿨롱의 법칙&lt;/strong&gt;&lt;br&gt;$\dfrac{1}{4 \pi \varepsilon_{0}} = 9 \times 10^{9}$ 라는 값을 통째로 외워 둔다. &lt;strong&gt;1 [C] 은 실제로는 엄청나게 큰 전하량&lt;/strong&gt;이라 이런 터무니없는 힘이 나온다 — &lt;strong&gt;정전기가 왜 위험한지&lt;/strong&gt;를 보여 준다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $F = 9 \times 10^{9} \times \dfrac{Q_{1} Q_{2}}{r^{2}}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;쿨롱의 법칙&lt;/strong&gt;&lt;br&gt;$\dfrac{1}{4 \pi \varepsilon_{0}} = 9 \times 10^{9}$라는 값을 통째로 외워 둔다. &lt;strong&gt;1 [C]은 실제로는 엄청나게 큰 전하량&lt;/strong&gt;이라 이런 터무니없는 힘이 나온다 — &lt;strong&gt;정전기가 왜 위험한지&lt;/strong&gt;를 보여 준다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $F = 9 \times 10^{9} \times \dfrac{Q_{1} Q_{2}}{r^{2}}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누전경보기의 설치&lt;/strong&gt;&lt;br&gt;일반 장소에서는 &lt;strong&gt;알리는 것(경보)&lt;/strong&gt;으로 충분하지만, &lt;strong&gt;불붙을 것이 이미 깔려 있는 곳에서는 끊어야(차단)&lt;/strong&gt; 한다. &lt;strong&gt;위험이 클수록 대책이 한 단계 더 나아간다&lt;/strong&gt;는 일관된 얼개다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가연성 증기가 있으면 차단기구까지&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누전경보기의 설치&lt;/strong&gt;&lt;br&gt;일반 장소에서는 &lt;strong&gt;알리는 것(경보)&lt;/strong&gt;으로 충분하지만, &lt;strong&gt;불붙을 것이 이미 깔려 있는 곳에서는 끊어야(차단)&lt;/strong&gt;한다. &lt;strong&gt;위험이 클수록 대책이 한 단계 더 나아간다&lt;/strong&gt;는 일관된 얼개다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가연성 증기가 있으면 차단기구까지&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11114,17 +11114,17 @@
       </c>
       <c r="AG78" s="32" t="inlineStr">
         <is>
-          <t>$\text{여유도} = \dfrac{\text{충격절연강도} - \text{제한전압}}{\text{제한전압}} \times 100$ 이므로 $0.33 = \dfrac{1 {,} 000 - V}{V}$ 다. $1.33 V = 1 {,} 000$ 에서 $V \fallingdotseq 752$ [kV] 다.</t>
+          <t>$\text{여유도} = \dfrac{\text{충격절연강도} - \text{제한전압}}{\text{제한전압}} \times 100$이므로 $0.33 = \dfrac{1 {,} 000 - V}{V}$다. $1.33 V = 1 {,} 000$에서 $V \fallingdotseq 752$ [kV]다.</t>
         </is>
       </c>
       <c r="AH78" s="32" t="inlineStr">
         <is>
-          <t>① 852 [kV] 는 계산과 맞지 않는다.&lt;br&gt;③ 652 [kV] 도 맞지 않는다.&lt;br&gt;④ 552 [kV] 도 맞지 않는다.</t>
+          <t>① 852 [kV]는 계산과 맞지 않는다.&lt;br&gt;③ 652 [kV] 도 맞지 않는다.&lt;br&gt;④ 552 [kV] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI78" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;피뢰기의 보호여유도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 제한전압&lt;/strong&gt;이므로 $V = \dfrac{\mathrm{BIL}}{1 + \text{여유도}}$ 로 한 번에 풀린다. &lt;strong&gt;충격절연강도로 나누면 670 [kV]&lt;/strong&gt;이 나와 오답이 되므로, &lt;strong&gt;어느 쪽이 분모인지&lt;/strong&gt;를 먼저 확인한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\text{제한전압} = \mathrm{BIL} \div ( 1 + \text{여유도} )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;피뢰기의 보호여유도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 제한전압&lt;/strong&gt;이므로 $V = \dfrac{\mathrm{BIL}}{1 + \text{여유도}}$로 한 번에 풀린다. &lt;strong&gt;충격절연강도로 나누면 670 [kV]&lt;/strong&gt;이 나와 오답이 되므로, &lt;strong&gt;어느 쪽이 분모인지&lt;/strong&gt;를 먼저 확인한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\text{제한전압} = \mathrm{BIL} \div ( 1 + \text{여유도} )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AG80" s="32" t="inlineStr">
         <is>
-          <t>유효 접속면의 깊이는 &lt;strong&gt;5산 이상(약 8 [mm] 이상)&lt;/strong&gt; 이라야 한다. &lt;strong&gt;5 [mm] 로는 화염이 새어 나갈&lt;/strong&gt; 수 있다.</t>
+          <t>유효 접속면의 깊이는 &lt;strong&gt;5산 이상(약 8 [mm] 이상)&lt;/strong&gt;이라야 한다. &lt;strong&gt;5 [mm] 로는 화염이 새어 나갈&lt;/strong&gt; 수 있다.</t>
         </is>
       </c>
       <c r="AH80" s="32" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="AG81" s="32" t="inlineStr">
         <is>
-          <t>이황화탄소처럼 위험한 것은 &lt;strong&gt;1 [m/s] 이하&lt;/strong&gt;로 제한한다. 5 [m/s] 는 너무 빠르다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험물 주입 시의 유속 제한&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;유속&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저항률 &lt;/u&gt;$10^{10}$&lt;u&gt; [Ω·cm] 미만의 도전성 위험물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 [m/s] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전하가 잘 빠진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저항률 &lt;/u&gt;$10^{10}$&lt;u&gt; [Ω·cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관 내경에 따라&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.05 [m] 면 3.5 [m/s] 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물이나 기체를 혼합하는 비수용성 위험물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m/s] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에테르 · 이황화탄소 등 위험성이 높은 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m/s] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m/s] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>이황화탄소처럼 위험한 것은 &lt;strong&gt;1 [m/s] 이하&lt;/strong&gt;로 제한한다. 5 [m/s]는 너무 빠르다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험물 주입 시의 유속 제한&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;유속&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저항률 &lt;/u&gt;$10^{10}$&lt;u&gt; [Ω·cm] 미만의 도전성 위험물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 [m/s] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전하가 잘 빠진다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저항률 &lt;/u&gt;$10^{10}$&lt;u&gt; [Ω·cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관 내경에 따라&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.05 [m] 면 3.5 [m/s] 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물이나 기체를 혼합하는 비수용성 위험물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m/s] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에테르 · 이황화탄소 등 위험성이 높은 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m/s] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m/s]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH81" s="32" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="AG83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;탄화칼슘(CaC₂, 카바이드)&lt;/strong&gt;이다. $\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$ 로 &lt;strong&gt;아세틸렌&lt;/strong&gt;이 난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금수성 물질과 물의 반응 생성물&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;생성 가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;반응식&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화칼슘 CaC₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세틸렌 C₂H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화알루미늄 Al₄C₃&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;메탄 CH₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나트륨 Na · 칼륨 K&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화칼슘 Ca₃P₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;포스핀 PH₃&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소화나트륨 NaH&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;탄화칼슘(CaC₂, 카바이드)&lt;/strong&gt;이다. $\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$로 &lt;strong&gt;아세틸렌&lt;/strong&gt;이 난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금수성 물질과 물의 반응 생성물&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;생성 가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;반응식&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화칼슘 CaC₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세틸렌 C₂H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화알루미늄 Al₄C₃&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;메탄 CH₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나트륨 Na · 칼륨 K&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화칼슘 Ca₃P₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;포스핀 PH₃&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소화나트륨 NaH&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH83" s="32" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="AH84" s="32" t="inlineStr">
         <is>
-          <t>① Burn-out point 는 열유속이 최대가 되는 점을 가리킨다.&lt;br&gt;③ Entrainment point 는 액적이 기류에 실려 나가는 점이다.&lt;br&gt;④ Sub-cooling boiling 은 액체 본체가 포화온도 아래인 상태의 비등이다.</t>
+          <t>① Burn-out point는 열유속이 최대가 되는 점을 가리킨다.&lt;br&gt;③ Entrainment point는 액적이 기류에 실려 나가는 점이다.&lt;br&gt;④ Sub-cooling boiling은 액체 본체가 포화온도 아래인 상태의 비등이다.</t>
         </is>
       </c>
       <c r="AI84" s="32" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>① 메탄이 가장 간단한 탄화수소이며 온실효과가 있는 것은 맞다.&lt;br&gt;② 프로판의 폭발범위 2.1 ~ 9.5 [%] 와 공기보다 무거운 것도 맞다.&lt;br&gt;④ 수소가 물에 잘 녹지 않고 온도가 오르면 반응성이 커지는 것도 맞다.</t>
+          <t>① 메탄이 가장 간단한 탄화수소이며 온실효과가 있는 것은 맞다.&lt;br&gt;② 프로판의 폭발범위 2.1 ~ 9.5 [%]와 공기보다 무거운 것도 맞다.&lt;br&gt;④ 수소가 물에 잘 녹지 않고 온도가 오르면 반응성이 커지는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="U89" s="32" t="inlineStr">
         <is>
-          <t>메탄 20%, 에탄 40%, 프로판 40%로 구성된 혼합가스가 공기 중에서 연소할 때 이 혼합가스의 이론적 화학양론 조성은 약 몇 % 인가? (단, 메탄, 에탄, 프로판의 양론농도(Cst)는 각각 9.5%, 5.6%, 4.0% 이다.)</t>
+          <t>메탄 20%, 에탄 40%, 프로판 40%로 구성된 혼합가스가 공기 중에서 연소할 때 이 혼합가스의 이론적 화학양론 조성은 약 몇 % 인가? (단, 메탄, 에탄, 프로판의 양론농도(Cst)는 각각 9.5%, 5.6%, 4.0%이다.)</t>
         </is>
       </c>
       <c r="V89" s="32" t="inlineStr"/>
@@ -12525,12 +12525,12 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>르 샤틀리에 식을 그대로 쓴다. $\dfrac{100}{C_{\mathrm{st}}} = \dfrac{20}{9.5} + \dfrac{40}{5.6} + \dfrac{40}{4.0} = 2.105 + 7.143 + 10 = 19.25$ 이므로 $C_{\mathrm{st}} = 100 / 19.25 \fallingdotseq 5.2$ [%] 다.</t>
+          <t>르 샤틀리에 식을 그대로 쓴다. $\dfrac{100}{C_{\mathrm{st}}} = \dfrac{20}{9.5} + \dfrac{40}{5.6} + \dfrac{40}{4.0} = 2.105 + 7.143 + 10 = 19.25$이므로 $C_{\mathrm{st}} = 100 / 19.25 \fallingdotseq 5.2$ [%]다.</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>② 7.7 [%] 는 세 값의 산술평균에 가까운 값으로 계산과 맞지 않는다.&lt;br&gt;③ 9.5 [%] 는 메탄 하나의 값이다.&lt;br&gt;④ 12.1 [%] 도 맞지 않는다.</t>
+          <t>② 7.7 [%]는 세 값의 산술평균에 가까운 값으로 계산과 맞지 않는다.&lt;br&gt;③ 9.5 [%]는 메탄 하나의 값이다.&lt;br&gt;④ 12.1 [%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세틸렌&lt;/strong&gt;이다. $\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$ 다.</t>
+          <t>&lt;strong&gt;아세틸렌&lt;/strong&gt;이다. $\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$다.</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AI94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;탄화칼슘(카바이드)과 물의 반응&lt;/strong&gt;&lt;br&gt;81번과 같은 반응이다. 이 때문에 &lt;strong&gt;카바이드는 물기를 철저히 피해 저장&lt;/strong&gt; 하고, &lt;strong&gt;아세틸렌 발생기실은 따로 두어 폭발에 대비&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;카바이드 + 물 → 아세틸렌&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;탄화칼슘(카바이드)과 물의 반응&lt;/strong&gt;&lt;br&gt;81번과 같은 반응이다. 이 때문에 &lt;strong&gt;카바이드는 물기를 철저히 피해 저장&lt;/strong&gt;하고, &lt;strong&gt;아세틸렌 발생기실은 따로 두어 폭발에 대비&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;카바이드 + 물 → 아세틸렌&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13437,7 +13437,7 @@
       </c>
       <c r="AH96" s="32" t="inlineStr">
         <is>
-          <t>① check valve(체크밸브)는 역류를 막는 밸브다.&lt;br&gt;③ vent stack 은 압력을 대기로 뿜어내는 굴뚝이다.&lt;br&gt;④ rupture disk(파열판)는 찢어져 압력을 빼는 판이다.</t>
+          <t>① check valve(체크밸브)는 역류를 막는 밸브다.&lt;br&gt;③ vent stack은 압력을 대기로 뿜어내는 굴뚝이다.&lt;br&gt;④ rupture disk(파열판)는 찢어져 압력을 빼는 판이다.</t>
         </is>
       </c>
       <c r="AI96" s="32" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="AI100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;석유화재(액면화재)의 거동&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;작은 불은 곱게(층류), 큰 불은 어지럽게(난류)&lt;/strong&gt; 탄다. 지름이 커지면 &lt;strong&gt;부력에 의한 상승기류가 세져&lt;/strong&gt; 화염이 흐트러진다. &lt;strong&gt;1 [m] 가 그 경계&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지름 1 [m] 이상이면 난류 화염&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;석유화재(액면화재)의 거동&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;작은 불은 곱게(층류), 큰 불은 어지럽게(난류)&lt;/strong&gt; 탄다. 지름이 커지면 &lt;strong&gt;부력에 의한 상승기류가 세져&lt;/strong&gt; 화염이 흐트러진다. &lt;strong&gt;1 [m]가 그 경계&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지름 1 [m] 이상이면 난류 화염&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="U101" s="32" t="inlineStr">
         <is>
-          <t>8vol% 헥산, 3vol% 메탄, 1vol% 에틸렌으로 구성된 혼합가스의 연소하한값(LFL)은 약 몇 vol% 인가? (단, 각 물질의 공기 중 연소하한값은 헥산은 1.1vol%, 메탄은 5.0vol%, 에틸렌은 2.7vol% 이다.)</t>
+          <t>8vol% 헥산, 3vol% 메탄, 1vol% 에틸렌으로 구성된 혼합가스의 연소하한값(LFL)은 약 몇 vol% 인가? (단, 각 물질의 공기 중 연소하한값은 헥산은 1.1vol%, 메탄은 5.0vol%, 에틸렌은 2.7vol%이다.)</t>
         </is>
       </c>
       <c r="V101" s="32" t="inlineStr"/>
@@ -14077,17 +14077,17 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>가연성 가스만으로 다시 100 [%] 로 잡는다. 합이 12 [vol%] 이므로 헥산 66.7, 메탄 25, 에틸렌 8.3 [%] 다. $\dfrac{100}{L} = \dfrac{66.7}{1.1} + \dfrac{25}{5.0} + \dfrac{8.3}{2.7} = 60.6 + 5 + 3.09 = 68.7$ 이므로 $L = 100 / 68.7 \fallingdotseq 1.45$ [vol%] 다.</t>
+          <t>가연성 가스만으로 다시 100 [%]로 잡는다. 합이 12 [vol%]이므로 헥산 66.7, 메탄 25, 에틸렌 8.3 [%]다. $\dfrac{100}{L} = \dfrac{66.7}{1.1} + \dfrac{25}{5.0} + \dfrac{8.3}{2.7} = 60.6 + 5 + 3.09 = 68.7$이므로 $L = 100 / 68.7 \fallingdotseq 1.45$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>① 0.69 [vol%] 는 환산을 잘못했을 때 나온다.&lt;br&gt;③ 1.95 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;④ 2.45 [vol%] 도 맞지 않는다.</t>
+          <t>① 0.69 [vol%]는 환산을 잘못했을 때 나온다.&lt;br&gt;③ 1.95 [vol%]는 계산과 맞지 않는다.&lt;br&gt;④ 2.45 [vol%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에(Le Chatelier)의 법칙&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$ 다. &lt;strong&gt;공기가 섞여 있으면 반드시 가연성 가스끼리 다시 100 [%] 로 환산&lt;/strong&gt; 한다. &lt;strong&gt;결과는 늘 가장 낮은 하한값(1.1)보다 조금 큰 값&lt;/strong&gt;이 되므로 검산이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기를 빼고 다시 100 [%] 로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에(Le Chatelier)의 법칙&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$다. &lt;strong&gt;공기가 섞여 있으면 반드시 가연성 가스끼리 다시 100 [%]로 환산&lt;/strong&gt;한다. &lt;strong&gt;결과는 늘 가장 낮은 하한값(1.1)보다 조금 큰 값&lt;/strong&gt;이 되므로 검산이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기를 빼고 다시 100 [%]로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>① 달기 와이어로프는 5 가 아니라 10 이상이다.&lt;br&gt;② 달기 강선도 10 이상이다.&lt;br&gt;③ 달기 체인은 3 이 아니라 5 이상이다.</t>
+          <t>① 달기 와이어로프는 5가 아니라 10 이상이다.&lt;br&gt;② 달기 강선도 10 이상이다.&lt;br&gt;③ 달기 체인은 3이 아니라 5 이상이다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="AI104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30 과 15&lt;/strong&gt;를 짝으로 잡는다 — &lt;strong&gt;경사는 30° 까지 허용하되, 15° 를 넘으면 미끄럼 방지&lt;/strong&gt;를 더한다. &lt;strong&gt;두 숫자를 서로 바꾸거나 20 으로 낮춰 놓는 것&lt;/strong&gt;이 단골이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 이하, 15 넘으면 미끄럼 방지&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt;▶  2. 경사는 30도 &lt;strong&gt;이하로 할 것&lt;/strong&gt;. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt; 5. 수직갱에 가설된 통로의 길이가 15미터 이상인 경우에는 10미터 이내마다 계단참을 설치할 것&lt;br&gt; 6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 이내마다 계단참을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30과 15&lt;/strong&gt;를 짝으로 잡는다 — &lt;strong&gt;경사는 30° 까지 허용하되, 15° 를 넘으면 미끄럼 방지&lt;/strong&gt;를 더한다. &lt;strong&gt;두 숫자를 서로 바꾸거나 20으로 낮춰 놓는 것&lt;/strong&gt;이 단골이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 이하, 15 넘으면 미끄럼 방지&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt;▶  2. 경사는 30도 &lt;strong&gt;이하로 할 것&lt;/strong&gt;. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt; 5. 수직갱에 가설된 통로의 길이가 15미터 이상인 경우에는 10미터 이내마다 계단참을 설치할 것&lt;br&gt; 6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 이내마다 계단참을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>② 320 [kgf] 는 어느 칸에도 없다.&lt;br&gt;③ 400 [kgf] 도 없다.&lt;br&gt;④ 500 [kgf] 도 없다.</t>
+          <t>② 320 [kgf]는 어느 칸에도 없다.&lt;br&gt;③ 400 [kgf] 도 없다.&lt;br&gt;④ 500 [kgf] 도 없다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="AH114" s="32" t="inlineStr">
         <is>
-          <t>② 40 [cm] 는 작업발판의 폭 기준이다.&lt;br&gt;③ 50 [cm] 라는 기준은 없다.&lt;br&gt;④ 60 [cm] 는 사다리 상단이 올라가야 할 길이다.</t>
+          <t>② 40 [cm]는 작업발판의 폭 기준이다.&lt;br&gt;③ 50 [cm]라는 기준은 없다.&lt;br&gt;④ 60 [cm]는 사다리 상단이 올라가야 할 길이다.</t>
         </is>
       </c>
       <c r="AI114" s="32" t="inlineStr">
@@ -15883,17 +15883,17 @@
       </c>
       <c r="AG115" s="32" t="inlineStr">
         <is>
-          <t>$H &amp;gt; \text{로프길이} + \text{로프의 늘어난 길이} + \dfrac{\text{신장}}{2} = 2 + ( 2 \times 0.3 ) + \dfrac{1.8}{2} = 2 + 0.6 + 0.9 = 3.5$ [m] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전대 고정점 높이의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;로프 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;로프의 늘어난 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 × 0.3 = 0.6 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;신율 30 [%]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신장의 1/2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8 ÷ 2 = 0.9 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;허리에서 발까지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.5 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;H 가 이보다 커야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$H &amp;gt; \text{로프길이} + \text{로프의 늘어난 길이} + \dfrac{\text{신장}}{2} = 2 + ( 2 \times 0.3 ) + \dfrac{1.8}{2} = 2 + 0.6 + 0.9 = 3.5$ [m]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전대 고정점 높이의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;로프 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;로프의 늘어난 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 × 0.3 = 0.6 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;신율 30 [%]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신장의 1/2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8 ÷ 2 = 0.9 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;허리에서 발까지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.5 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;H가 이보다 커야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH115" s="32" t="inlineStr">
         <is>
-          <t>① 1.5 [m] 는 로프 길이에도 못 미친다.&lt;br&gt;② 2.5 [m] 는 신장의 1/2 을 빠뜨린 값이다.&lt;br&gt;④ 4.5 [m] 는 신장 전체를 더한 값에 가깝다.</t>
+          <t>① 1.5 [m]는 로프 길이에도 못 미친다.&lt;br&gt;② 2.5 [m]는 신장의 1/2을 빠뜨린 값이다.&lt;br&gt;④ 4.5 [m]는 신장 전체를 더한 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI115" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전대 고정점의 최소 높이&lt;/strong&gt;&lt;br&gt;세 값을 더한다 — &lt;strong&gt;로프 길이 + 늘어남 + 신장의 절반&lt;/strong&gt;. &lt;strong&gt;신장의 「절반」인 까닭은 안전대를 허리에 매기 때문&lt;/strong&gt;이다. 온몸 길이를 더하면 4.4 [m] 가 되어 오답이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;로프 + 늘어남 + 신장의 절반&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전대 고정점의 최소 높이&lt;/strong&gt;&lt;br&gt;세 값을 더한다 — &lt;strong&gt;로프 길이 + 늘어남 + 신장의 절반&lt;/strong&gt;. &lt;strong&gt;신장의 「절반」인 까닭은 안전대를 허리에 매기 때문&lt;/strong&gt;이다. 온몸 길이를 더하면 4.4 [m]가 되어 오답이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;로프 + 늘어남 + 신장의 절반&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="AG119" s="32" t="inlineStr">
         <is>
-          <t>점화회선은 &lt;strong&gt;다른 동력선·조명회선과 완전히 분리&lt;/strong&gt; 해야 한다. 한곳에 모으면 &lt;strong&gt;유도전류로 뜻하지 않게 터질 수&lt;/strong&gt; 있다.</t>
+          <t>점화회선은 &lt;strong&gt;다른 동력선·조명회선과 완전히 분리&lt;/strong&gt;해야 한다. 한곳에 모으면 &lt;strong&gt;유도전류로 뜻하지 않게 터질 수&lt;/strong&gt; 있다.</t>
         </is>
       </c>
       <c r="AH119" s="32" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="AG120" s="32" t="inlineStr">
         <is>
-          <t>매다는 각도는 &lt;strong&gt;60° 이내&lt;/strong&gt; 라야 한다. &lt;strong&gt;각도가 벌어질수록 줄에 걸리는 장력이 급격히 커진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;매다는 각도와 줄 하나에 걸리는 장력&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;각도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장력 배수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.50 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;두 줄이 나란히&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.52 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;60°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.58 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기까지 허용&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;90°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.71 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;120°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.00 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;줄 하나로 드는 것과 같다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;150°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.93 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>매다는 각도는 &lt;strong&gt;60° 이내&lt;/strong&gt;라야 한다. &lt;strong&gt;각도가 벌어질수록 줄에 걸리는 장력이 급격히 커진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;매다는 각도와 줄 하나에 걸리는 장력&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;각도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장력 배수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.50 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;두 줄이 나란히&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.52 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;60°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.58 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기까지 허용&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;90°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.71 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;120°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.00 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;줄 하나로 드는 것과 같다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;150°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.93 배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH120" s="32" t="inlineStr">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="AG122" s="32" t="inlineStr">
         <is>
-          <t>버팀줄만으로 세울 때는 &lt;strong&gt;3개 이상&lt;/strong&gt; 이라야 한다. 2개로는 &lt;strong&gt;한 방향으로 넘어가는 것을 막지 못한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;항타기·항발기의 무너짐 방지 (규칙 제209조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연약한 지반에는 깔판·깔목 등을 사용해 침하를 막을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시설이나 가설물 위에 설치할 때는 그 내력을 확인하고 부족하면 보강할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;각부나 가대가 미끄러질 우려가 있으면 말뚝이나 쐐기로 고정할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀대만으로 상단을 안정시킬 때는 버팀대를 3개 이상으로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀줄만으로 상단을 안정시킬 때는 버팀줄을 3개 이상으로 하고 같은 간격으로 배치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;평형추는 이동하지 않도록 가대에 견고히 부착할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>버팀줄만으로 세울 때는 &lt;strong&gt;3개 이상&lt;/strong&gt;이라야 한다. 2개로는 &lt;strong&gt;한 방향으로 넘어가는 것을 막지 못한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;항타기·항발기의 무너짐 방지 (규칙 제209조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연약한 지반에는 깔판·깔목 등을 사용해 침하를 막을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시설이나 가설물 위에 설치할 때는 그 내력을 확인하고 부족하면 보강할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;각부나 가대가 미끄러질 우려가 있으면 말뚝이나 쐐기로 고정할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀대만으로 상단을 안정시킬 때는 버팀대를 3개 이상으로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀줄만으로 상단을 안정시킬 때는 버팀줄을 3개 이상으로 하고 같은 간격으로 배치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;평형추는 이동하지 않도록 가대에 견고히 부착할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH122" s="32" t="inlineStr">
